--- a/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 13,84</t>
+          <t>3,64; 13,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 16,19</t>
+          <t>6,59; 15,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,82</t>
+          <t>6,04; 12,65</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,3</t>
+          <t>8,8; 17,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,85</t>
+          <t>6,16; 14,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,36; 14,18</t>
+          <t>8,72; 14,56</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,37</t>
+          <t>8,35; 13,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,28</t>
+          <t>5,05; 9,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,58</t>
+          <t>7,15; 10,66</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,57</t>
+          <t>2,19; 8,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,81</t>
+          <t>8,76; 13,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,07</t>
+          <t>4,72; 10,09</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,39</t>
+          <t>6,97; 11,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,46</t>
+          <t>8,64; 12,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,31</t>
+          <t>8,24; 11,28</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,82</t>
+          <t>7,91; 13,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 74,2</t>
+          <t>6,87; 75,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,45; 65,81</t>
+          <t>8,41; 61,22</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,95</t>
+          <t>6,81; 12,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,3</t>
+          <t>8,15; 12,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,35</t>
+          <t>8,11; 11,35</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,14</t>
+          <t>6,84; 10,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 32,74</t>
+          <t>9,24; 30,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,86; 21,95</t>
+          <t>8,88; 20,44</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15295; 55353</t>
+          <t>14552; 53041</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20618; 50713</t>
+          <t>20631; 49080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42012; 91447</t>
+          <t>43064; 90192</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39185; 73276</t>
+          <t>37278; 75744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31431; 70944</t>
+          <t>31523; 72464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78182; 132628</t>
+          <t>81583; 136252</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45749; 77072</t>
+          <t>44783; 74729</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30148; 54852</t>
+          <t>29858; 54582</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81547; 119308</t>
+          <t>80611; 120167</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18585; 76021</t>
+          <t>19439; 74516</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63500; 98377</t>
+          <t>62373; 97777</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67057; 161009</t>
+          <t>75512; 161265</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39387; 63941</t>
+          <t>39122; 64757</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47110; 68217</t>
+          <t>47290; 69571</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91085; 125429</t>
+          <t>91289; 125066</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29020; 47213</t>
+          <t>29108; 48482</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41457; 450976</t>
+          <t>41774; 458785</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82491; 642307</t>
+          <t>82123; 597483</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18910; 33790</t>
+          <t>19261; 34577</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34155; 52396</t>
+          <t>34724; 52015</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57719; 80451</t>
+          <t>57445; 80451</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>239361; 350675</t>
+          <t>236586; 347832</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>345188; 1214652</t>
+          <t>342711; 1145201</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>634823; 1573330</t>
+          <t>636630; 1465444</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,26</t>
+          <t>3,94; 13,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 15,67</t>
+          <t>8,05; 17,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 12,65</t>
+          <t>7,28; 13,88</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 17,88</t>
+          <t>9,18; 17,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,15</t>
+          <t>9,86; 16,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,56</t>
+          <t>10,27; 15,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 13,94</t>
+          <t>9,2; 14,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,23</t>
+          <t>6,28; 9,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,66</t>
+          <t>8,56; 11,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,4</t>
+          <t>6,47; 10,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,73</t>
+          <t>9,29; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 10,09</t>
+          <t>8,39; 11,2</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,54</t>
+          <t>7,0; 11,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,71</t>
+          <t>8,89; 12,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,28</t>
+          <t>8,53; 11,6</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 13,17</t>
+          <t>8,31; 13,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 75,48</t>
+          <t>6,07; 9,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,41; 61,22</t>
+          <t>7,63; 10,88</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,23</t>
+          <t>6,82; 12,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,22</t>
+          <t>7,96; 12,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,35</t>
+          <t>8,19; 11,53</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,06</t>
+          <t>9,02; 11,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,87</t>
+          <t>9,47; 11,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,88; 20,44</t>
+          <t>9,47; 10,99</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>32942</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32688</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62501</t>
+          <t>76922</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14552; 53041</t>
+          <t>16070; 53112</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20631; 49080</t>
+          <t>29199; 62671</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43064; 90192</t>
+          <t>56041; 106880</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>60109</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53765</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108055</t>
+          <t>125073</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37278; 75744</t>
+          <t>43769; 81148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31523; 72464</t>
+          <t>49453; 81091</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81583; 136252</t>
+          <t>100512; 149417</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59162</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41874</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101036</t>
+          <t>123738</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44783; 74729</t>
+          <t>57000; 90440</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29858; 54582</t>
+          <t>39003; 61574</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80611; 120167</t>
+          <t>106192; 146693</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>48998</t>
+          <t>58182</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>78663</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127661</t>
+          <t>139243</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19439; 74516</t>
+          <t>45274; 74059</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62373; 97777</t>
+          <t>68423; 95776</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75512; 161265</t>
+          <t>120499; 160811</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>50620</t>
+          <t>55283</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57484</t>
+          <t>66450</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108103</t>
+          <t>121734</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39122; 64757</t>
+          <t>42639; 70261</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47290; 69571</t>
+          <t>54083; 78613</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91289; 125066</t>
+          <t>103822; 141265</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>234952</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273008</t>
+          <t>77507</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29108; 48482</t>
+          <t>33828; 55436</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41774; 458785</t>
+          <t>26634; 42526</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82123; 597483</t>
+          <t>64534; 91990</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>41984</t>
+          <t>46369</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68003</t>
+          <t>75151</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19261; 34577</t>
+          <t>21156; 37756</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34724; 52015</t>
+          <t>36992; 56629</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57445; 80451</t>
+          <t>63421; 89301</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>306958</t>
+          <t>353173</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>541409</t>
+          <t>386194</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>848367</t>
+          <t>739367</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>236586; 347832</t>
+          <t>318421; 394750</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>342711; 1145201</t>
+          <t>353518; 423867</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>636630; 1465444</t>
+          <t>687566; 798216</t>
         </is>
       </c>
     </row>
